--- a/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
+++ b/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
@@ -833,7 +833,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0RQQ00000HGGi9</t>
+          <t>a0R3g0000095RL1</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a0R3g0000095RL1</t>
+          <t>a0RQQ00000HGGi9</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>a0RQQ00000HxIaD</t>
+          <t>a0R3g0000095ROt</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1593,7 +1593,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>a0R3g0000095ROt</t>
+          <t>a0RQQ00000HxIaD</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1973,7 +1973,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>a0R60000000FqrH</t>
+          <t>a0R60000000FqrO</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1993,7 +1993,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>a0R60000000FqrL</t>
+          <t>a0R60000000FqrH</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2013,7 +2013,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a0R60000000FqrO</t>
+          <t>a0R60000000FqrL</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2253,7 +2253,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>a0R60000000GdAN</t>
+          <t>a0R60000000G0mJ</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MOSAIQ IGRT Connectivity for Varian</t>
+          <t>Connectivity to DICOM RT BrainLAB iPlan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2293,7 +2293,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>a0R60000000G0mJ</t>
+          <t>a0R60000000G0mL</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Connectivity to DICOM RT BrainLAB iPlan</t>
+          <t>Connectivity to Varian RapidArc VMAT</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>a0R60000000G0mL</t>
+          <t>a0R60000000GdAN</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Connectivity to Varian RapidArc VMAT</t>
+          <t>MOSAIQ IGRT Connectivity for Varian</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0U</t>
+          <t>a0R60000000Fz0K</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Morphology Reference</t>
+          <t>Code Update</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2573,15 +2573,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0K</t>
+          <t>a0R60000000Fz0R</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Code Update</t>
+          <t>ECHART USERS FOR RO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0L</t>
+          <t>a0R60000000Fz0N</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>EXTENDED BARCODING</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0M</t>
+          <t>a0R60000000Fz0U</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TNM Staging Reference</t>
+          <t>Morphology Reference</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2633,7 +2633,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0N</t>
+          <t>a0R60000000Fz0M</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EXTENDED BARCODING</t>
+          <t>TNM Staging Reference</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2653,15 +2653,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a0R60000000Fz0R</t>
+          <t>a0R60000000Fz0L</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECHART USERS FOR RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>a0R60000000sTpI</t>
+          <t>a0R60000000sTpG</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ESI: Charge Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a0R60000000GdDh</t>
+          <t>a0R60000000GdDq</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ESI: Charge Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2773,7 +2773,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a0R60000000sTpG</t>
+          <t>a0R60000000FuUh</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2793,7 +2793,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>a0R60000000GdDq</t>
+          <t>a0R60000000sTpI</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>ESI: Charge Export to TBD</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>a0R60000000FuUe</t>
+          <t>a0R60000000GdDh</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2833,7 +2833,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>a0R60000000FuUh</t>
+          <t>a0R60000000FuUe</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>ESI: Charge Export to TBD</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>a0RQQ00000KdjWP</t>
+          <t>a0RKf00000KeXnA</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -2893,7 +2893,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>a0RKf00000KeXnA</t>
+          <t>a0RQQ00000KdjWP</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2973,7 +2973,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>a0RKf00000KfaET</t>
+          <t>a0RQQ00000Izy9l</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2993,7 +2993,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>a0RQQ00000Izy9l</t>
+          <t>a0RKf00000KfaET</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>a0RQQ00000Kg4y9</t>
+          <t>a0R6g00000Hj0Ib</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3113,7 +3113,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a0R6g00000Hj0Ib</t>
+          <t>a0RQQ00000Kg4y9</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3273,7 +3273,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>a0RQQ00000HWUnZ</t>
+          <t>a0R3g00000AS80n</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>a0R3g00000AS80n</t>
+          <t>a0RQQ00000HWUnZ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4113,7 +4113,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>a0RKf00000ExomG</t>
+          <t>a0RQQ00000KkKY5</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>a0RQQ00000KkKY5</t>
+          <t>a0RKf00000ExomG</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>a0RKf00000ExrOW</t>
+          <t>a0R3g0000095N75</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MDD SOFTWARE</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>a0R3g0000095N75</t>
+          <t>a0RKf00000ExrOW</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4g</t>
+          <t>a0R60000000GdjZ</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>IQ Server</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>a0R60000000GdjZ</t>
+          <t>a0R60000000Fr4h</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -4853,7 +4853,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4h</t>
+          <t>a0R60000000Fr4i</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -4873,7 +4873,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>a0R60000000Fr4i</t>
+          <t>a0R60000000Gdjc</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4893,7 +4893,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>a0R60000000Gdjc</t>
+          <t>a0R60000000Fr4g</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>IQ Server</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>a0R60000004SFOV</t>
+          <t>a0R60000004SFPs</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>ESI: ADT Import from TBD</t>
+          <t>Connectivity to DICOM RT Elekta ERGO++</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>a0R60000004SFOf</t>
+          <t>a0R60000004SFQ7</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ESI IMPLEMENTATION SERVICES</t>
+          <t>Connectivity to non-DICOM from Varian PortalVision</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>a0R60000004SFP4</t>
+          <t>a0R60000004SFOV</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ESI: Schedule Export to TBD</t>
+          <t>ESI: ADT Import from TBD</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>a0R60000004SFPs</t>
+          <t>a0R60000004SFP4</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Connectivity to DICOM RT Elekta ERGO++</t>
+          <t>ESI: Schedule Export to TBD</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>a0R60000004SFQ7</t>
+          <t>a0R60000004SFOf</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Connectivity to non-DICOM from Varian PortalVision</t>
+          <t>ESI IMPLEMENTATION SERVICES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5453,7 +5453,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>a0R32000003IC7d</t>
+          <t>a0R32000003IC9e</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>IQ Server</t>
+          <t>Connectivity to Elekta VMAT</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5493,7 +5493,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>a0R32000003IC9e</t>
+          <t>a0R32000003IC7d</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Connectivity to Elekta VMAT</t>
+          <t>IQ Server</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6153,7 +6153,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>a0RQQ00000JV3eb</t>
+          <t>a0RQQ00000JQegP</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6173,7 +6173,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>a0RQQ00000JQegP</t>
+          <t>a0RQQ00000JV3eb</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>a0R60000000Fun1</t>
+          <t>a0R60000000Fun5</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>EXTENDED BARCODING</t>
+          <t>Code Update</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6253,7 +6253,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>a0R60000000Fun2</t>
+          <t>a0R60000000FunD</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Photos &amp; Diagrams</t>
+          <t>Document Management Package for RO</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6273,7 +6273,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>a0R60000000Fun3</t>
+          <t>a0R60000000Fun1</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TNM Staging Reference</t>
+          <t>EXTENDED BARCODING</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6293,7 +6293,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>a0R60000000Fun4</t>
+          <t>a0R60000000Fun2</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>Photos &amp; Diagrams</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6313,7 +6313,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>a0R60000000Fun5</t>
+          <t>a0R60000000Fun3</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Code Update</t>
+          <t>TNM Staging Reference</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6333,7 +6333,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>a0R60000000FunD</t>
+          <t>a0R60000000Fun4</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Document Management Package for RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>a0R60000000G153</t>
+          <t>a0R60000000G15F</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Topography Reference</t>
+          <t>Document Management Package for RO</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6473,7 +6473,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>a0R60000000G156</t>
+          <t>a0R60000000G15E</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>PhAST Note</t>
+          <t>ECHART USERS FOR RO</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6493,7 +6493,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>a0R60000000G15E</t>
+          <t>a0R60000000G156</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ECHART USERS FOR RO</t>
+          <t>PhAST Note</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>a0R60000000G15F</t>
+          <t>a0R60000000G153</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Document Management Package for RO</t>
+          <t>Topography Reference</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -6813,7 +6813,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>a0R60000000FuxK</t>
+          <t>a0R60000000FuxL</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>One-time TX Detail Import</t>
+          <t>One time Diagnosis Detail  Import</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -6833,7 +6833,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>a0R60000000FuxL</t>
+          <t>a0R60000000FuxK</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>One time Diagnosis Detail  Import</t>
+          <t>One-time TX Detail Import</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7413,7 +7413,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>a0RQQ00000HEosn</t>
+          <t>a0RQQ00000HEpFN</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7433,7 +7433,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>a0RQQ00000HEpFN</t>
+          <t>a0RQQ00000HEosn</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>a0RQQ00000IyBr3</t>
+          <t>a0RQQ00000Iy4kn</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>MOSAIQ Oncology Analytics</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>a0RQQ00000Iy4kn</t>
+          <t>a0RQQ00000IyBr3</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Oncology Analytics</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>a0RQQ00000InIO1</t>
+          <t>a0RKf00000KfTyQ</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -8853,7 +8853,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>a0RKf00000KfTyQ</t>
+          <t>a0RQQ00000InIO1</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -9993,7 +9993,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>a0RKf00000ExqhY</t>
+          <t>a0RQQ00000J1sBV</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -10013,7 +10013,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>a0RQQ00000J1sBV</t>
+          <t>a0RKf00000ExqhY</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -10993,7 +10993,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>a0RKf00000KfYgR</t>
+          <t>a0RQQ00000HdoKv</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA PREMIUM USER LICENSE SUBSC</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -11013,7 +11013,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>a0RQQ00000Hdo6P</t>
+          <t>a0RQQ00000IaqP7</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>MOSAIQ Oncology Analytics</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -11033,7 +11033,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>a0RQQ00000HdoKv</t>
+          <t>a0RQQ00000Hdo6P</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>MOA PREMIUM USER LICENSE SUBSC</t>
+          <t>MOSAIQ Oncology Analytics</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -11053,7 +11053,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>a0RQQ00000IaqP7</t>
+          <t>a0RKf00000KfYgR</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -11133,7 +11133,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>a0R60000000GbQz</t>
+          <t>a0R60000000GbN2</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Formulary Plus Canadian Version</t>
+          <t>Connectivity to Varian Truebeam 4D</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -11153,7 +11153,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>a0R60000000GbN2</t>
+          <t>a0R60000000GbQz</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Connectivity to Varian Truebeam 4D</t>
+          <t>Formulary Plus Canadian Version</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -11173,7 +11173,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>a0RQQ00000JWhV7</t>
+          <t>a0RQQ00000LDoNt</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -11193,7 +11193,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>a0RQQ00000HuIGb</t>
+          <t>a0RQQ00000JWhV7</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -11213,7 +11213,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>a0RQQ00000LDoNt</t>
+          <t>a0RQQ00000HuIGb</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">

--- a/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
+++ b/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQknt</t>
+          <t>a0RQQ00000M8wAD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,19 +461,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10933_MOA02_2</t>
+          <t>10355_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXqtN</t>
+          <t>a0RQQ00000MPOTt</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -486,14 +486,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11385_MOA01_2</t>
+          <t>10491_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXr1R</t>
+          <t>a0RQQ00000LQknt</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -506,14 +506,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11558_PLZ01_2</t>
+          <t>10933_MOA02_2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXrEL</t>
+          <t>a0RQQ00000LXqtN</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -526,14 +526,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12015_PLZ01_2</t>
+          <t>11385_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjXoX</t>
+          <t>a0RQQ00000MOO69</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -541,19 +541,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12349_RO PLZ_2</t>
+          <t>11387_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0RQQ00000LRGSn</t>
+          <t>a0RQQ00000MPozR</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12579_RO02_2</t>
+          <t>11391_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYwdN</t>
+          <t>a0RQQ00000MQUc5</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -586,14 +586,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12667_RO02_2</t>
+          <t>11407_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXr6H</t>
+          <t>a0RQQ00000LXr1R</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -606,14 +606,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13169_RO00_2</t>
+          <t>11558_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQjNB</t>
+          <t>a0RQQ00000M4ffp</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -621,19 +621,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13519_MOA01_2</t>
+          <t>11628_RO001_2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYNNt</t>
+          <t>a0RQQ00000LXrEL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -646,14 +646,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14308_MOA01_2</t>
+          <t>12015_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYNVx</t>
+          <t>a0RQQ00000MORvF</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -666,14 +666,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14308_RO01_2</t>
+          <t>12122_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0RQQ00000LVSyP</t>
+          <t>a0RQQ00000LjXoX</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -681,19 +681,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MOSAIQ</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15182_OIS002_2</t>
+          <t>12349_RO PLZ_2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a0RQQ00000LZdvF</t>
+          <t>a0RQQ00000LRGSn</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17563_RO01_2</t>
+          <t>12579_RO02_2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQl8r</t>
+          <t>a0R60000001C62V</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -721,19 +721,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>Connectivity to DICOM PORT Import (TBD)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17595_MOA02_2</t>
+          <t>12598_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a0RQQ00000LhNWj</t>
+          <t>a0RQQ00000LYwdN</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -741,19 +741,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21100_PLZ001_2</t>
+          <t>12667_RO02_2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQgcD</t>
+          <t>a0RQQ00000LXr6H</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -766,14 +766,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30000116_PLZ01_2</t>
+          <t>13169_RO00_2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a0RQQ00000LbxOP</t>
+          <t>a0RQQ00000MRGdV</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -781,19 +781,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30002222_RO01_2</t>
+          <t>13519_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a0RQQ00000LT6XN</t>
+          <t>a0RQQ00000MPGJR</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -801,19 +801,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30002224_RO01_2</t>
+          <t>13727_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0RQQ00000LZlSz</t>
+          <t>a0RQQ00000MOMvZ</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -821,19 +821,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30002863_RO001_2</t>
+          <t>13743_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQiZB</t>
+          <t>a0RQQ00000MRJ57</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -846,14 +846,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30004005_PLZ01_2</t>
+          <t>13808_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQhq1</t>
+          <t>a0RQQ00000MRHRV</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -866,14 +866,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30004172_PLZ01_2</t>
+          <t>13852_EHA01_2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQkRJ</t>
+          <t>a0RQQ00000MRHZZ</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -886,14 +886,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30007309_PLZ01_2</t>
+          <t>13852_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQk9Z</t>
+          <t>a0RQQ00000LuYfd</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -906,7 +906,467 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>14117_MOA01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LYNNt</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14308_MOA01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LYNVx</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>14308_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LVSyP</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MOSAIQ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>15182_OIS002_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LyPIn</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>15238_RO00_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LZdvF</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>17563_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LQl8r</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>17595_MOA02_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MLxA5</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>19028_RO001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LhNWj</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SMARTCLINIC SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21100_PLZ001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LQgcD</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>30000116_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MRBKU</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>30000211_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MRMxR</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>30002148_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LbxOP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30002222_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LT6XN</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>30002224_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LZlSz</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MDD SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>30002863_RO001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LQiZB</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>30004005_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MPJHJ</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>30004172_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MPIQ5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>30006865_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MOQcb</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>30007309_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MKvqH</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>30007388_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MOPbh</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>30007741_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>a0RQQ00000M8uzd</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>30008081_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MR8T3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>30008509_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MNDUX</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>30008774_RO01_2</t>
         </is>
       </c>
     </row>

--- a/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
+++ b/Mass_update_MOSAIQ/mass_update_MOSAIQ_quantity_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQknt</t>
+          <t>a0RQQ00000MVKIj</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXqtN</t>
+          <t>a0RQQ00000MSMgr</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -526,14 +526,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11385_MOA01_2</t>
+          <t>11312_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0RQQ00000MOO69</t>
+          <t>a0RQQ00000LXqtN</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,14 +546,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11387_PLZ01_2</t>
+          <t>11385_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a0RQQ00000MPozR</t>
+          <t>a0RQQ00000MOO69</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11391_PLZ01_2</t>
+          <t>11387_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a0RQQ00000MQUc5</t>
+          <t>a0RQQ00000MPozR</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -581,19 +581,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11407_RO01_2</t>
+          <t>11391_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXr1R</t>
+          <t>a0RQQ00000MQUc5</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -601,19 +601,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11558_PLZ01_2</t>
+          <t>11407_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a0RQQ00000M4ffp</t>
+          <t>a0RQQ00000LXr1R</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -621,19 +621,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11628_RO001_2</t>
+          <t>11558_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXrEL</t>
+          <t>a0RQQ00000MVIlZ</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -646,14 +646,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12015_PLZ01_2</t>
+          <t>11564_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a0RQQ00000MORvF</t>
+          <t>a0RQQ00000MScqT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -666,14 +666,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12122_PLZ01_2</t>
+          <t>11596_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjXoX</t>
+          <t>a0RQQ00000MScvJ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -681,19 +681,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12349_RO PLZ_2</t>
+          <t>11596_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a0RQQ00000LRGSn</t>
+          <t>a0RQQ00000M4ffp</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -706,14 +706,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12579_RO02_2</t>
+          <t>11628_RO001_2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a0R60000001C62V</t>
+          <t>a0RQQ00000LXrEL</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -721,19 +721,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Connectivity to DICOM PORT Import (TBD)</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12598_RO01_2</t>
+          <t>12015_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYwdN</t>
+          <t>a0RQQ00000MORvF</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -741,19 +741,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12667_RO02_2</t>
+          <t>12122_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a0RQQ00000LXr6H</t>
+          <t>a0RQQ00000LjXoX</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -761,19 +761,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13169_RO00_2</t>
+          <t>12349_RO PLZ_2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRGdV</t>
+          <t>a0RQQ00000LRGSn</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -781,19 +781,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13519_MOA01_2</t>
+          <t>12579_RO02_2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a0RQQ00000MPGJR</t>
+          <t>a0R60000001C62V</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -801,19 +801,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>Connectivity to DICOM PORT Import (TBD)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13727_PLZ01_2</t>
+          <t>12598_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a0RQQ00000MOMvZ</t>
+          <t>a0RQQ00000MSS7x</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -826,14 +826,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13743_RO01_2</t>
+          <t>12615_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRJ57</t>
+          <t>a0RQQ00000MSSCn</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -846,14 +846,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13808_PLZ01_2</t>
+          <t>12615_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRHRV</t>
+          <t>a0RQQ00000LYwdN</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -861,19 +861,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13852_EHA01_2</t>
+          <t>12667_RO02_2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRHZZ</t>
+          <t>a0RQQ00000MVIOz</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -886,14 +886,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13852_PLZ01_2</t>
+          <t>12722_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a0RQQ00000LuYfd</t>
+          <t>a0RQQ00000LXr6H</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -906,14 +906,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14117_MOA01_2</t>
+          <t>13169_RO00_2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYNNt</t>
+          <t>a0RQQ00000MRGdV</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -926,14 +926,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>14308_MOA01_2</t>
+          <t>13519_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a0RQQ00000LYNVx</t>
+          <t>a0RQQ00000MPGJR</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -946,14 +946,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14308_RO01_2</t>
+          <t>13727_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a0RQQ00000LVSyP</t>
+          <t>a0RQQ00000MOMvZ</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -961,19 +961,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MOSAIQ</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15182_OIS002_2</t>
+          <t>13743_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a0RQQ00000LyPIn</t>
+          <t>a0RQQ00000MRJ57</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -981,19 +981,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15238_RO00_2</t>
+          <t>13808_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a0RQQ00000LZdvF</t>
+          <t>a0RQQ00000MRHRV</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17563_RO01_2</t>
+          <t>13852_EHA01_2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQl8r</t>
+          <t>a0RQQ00000MRHZZ</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1026,14 +1026,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17595_MOA02_2</t>
+          <t>13852_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a0RQQ00000MLxA5</t>
+          <t>a0RQQ00000LuYfd</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1041,19 +1041,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MOSAIQ Software</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19028_RO001_2</t>
+          <t>14117_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a0RQQ00000LhNWj</t>
+          <t>a0RQQ00000LYNNt</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SMARTCLINIC SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21100_PLZ001_2</t>
+          <t>14308_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQgcD</t>
+          <t>a0RQQ00000LYNVx</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1086,14 +1086,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30000116_PLZ01_2</t>
+          <t>14308_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRBKU</t>
+          <t>a0RQQ00000MSJ6I</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1106,14 +1106,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30000211_PLZ01_2</t>
+          <t>14598_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a0RQQ00000MRMxR</t>
+          <t>a0RQQ00000LVSyP</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1121,19 +1121,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>30002148_PLZ01_2</t>
+          <t>15182_OIS002_2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a0RQQ00000LbxOP</t>
+          <t>a0RQQ00000LyPIn</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1146,14 +1146,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>30002222_RO01_2</t>
+          <t>15238_RO00_2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a0RQQ00000LT6XN</t>
+          <t>a0RQQ00000LZdvF</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1166,14 +1166,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>30002224_RO01_2</t>
+          <t>17563_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a0RQQ00000LZlSz</t>
+          <t>a0RQQ00000LQl8r</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1181,19 +1181,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDD SOFTWARE</t>
+          <t>MOA Software</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30002863_RO001_2</t>
+          <t>17595_MOA02_2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>a0RQQ00000LQiZB</t>
+          <t>a0RQQ00000MVJHp</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1206,14 +1206,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30004005_PLZ01_2</t>
+          <t>18024_MOA01_2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>a0RQQ00000MPJHJ</t>
+          <t>a0RQQ00000MLxA5</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30004172_PLZ01_2</t>
+          <t>19028_RO001_2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a0RQQ00000MPIQ5</t>
+          <t>a0RQQ00000LhNWj</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1241,19 +1241,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>SMARTCLINIC SOFTWARE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>30006865_PLZ01_2</t>
+          <t>21100_PLZ001_2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a0RQQ00000MOQcb</t>
+          <t>a0RQQ00000LQgcD</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30007309_PLZ01_2</t>
+          <t>30000116_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a0RQQ00000MKvqH</t>
+          <t>a0RQQ00000MRBKU</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1286,14 +1286,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30007388_PLZ01_2</t>
+          <t>30000211_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a0RQQ00000MOPbh</t>
+          <t>a0RQQ00000MRMxR</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>30007741_PLZ01_2</t>
+          <t>30002148_PLZ01_2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>a0RQQ00000M8uzd</t>
+          <t>a0RQQ00000LbxOP</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1326,14 +1326,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>30008081_RO01_2</t>
+          <t>30002222_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a0RQQ00000MR8T3</t>
+          <t>a0RQQ00000LT6XN</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1341,30 +1341,250 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MOA Software</t>
+          <t>MOSAIQ Software</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30008509_PLZ01_2</t>
+          <t>30002224_RO01_2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>a0RQQ00000LZlSz</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MDD SOFTWARE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>30002863_RO001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LQiZB</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>30004005_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MPJHJ</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>30004172_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MVeFp</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>30005173_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MPIQ5</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>30006865_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MOQcb</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>30007309_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MKvqH</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>30007388_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MSP3d</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>30007730_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MOPbh</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>30007741_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>a0RQQ00000M8uzd</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MOSAIQ Software</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>30008081_RO01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MR8T3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MOA Software</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>30008509_PLZ01_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>a0RQQ00000MNDUX</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>MOSAIQ Software</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>30008774_RO01_2</t>
         </is>
